--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,6 +151,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -593,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -618,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -638,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.951</v>
+        <v>0.946</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -654,7 +656,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -687,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>61.93</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -732,52 +734,67 @@
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -788,6 +805,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -795,7 +813,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -862,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0445300006866455</v>
+        <v>0.0447700023651123</v>
       </c>
     </row>
     <row r="6">
@@ -1191,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540364.41143226</v>
+        <v>52540362.32258064</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>61.93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1491,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3253824768</v>
+        <v>3257502464</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>6.78</v>
@@ -1503,56 +1520,250 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ALK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alaska Air Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>4993132544</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>91.44898000000001</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>0.696</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BCO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Brinks Company (The)</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>4231350528</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>24.007008</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>8.406000000000001</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>1.361</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Avis Budget Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>6170568192</v>
+      </c>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Everus Construction Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>7231064576</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>32.418766</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>23.896</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>1.941</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ENS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EnerSys</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>8254842368</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>29.319067</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>15.631</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LNZA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LanzaTech Global, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>79713008</v>
+      </c>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n">
+        <v>-1.301</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>1.192</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Industrial Direct Company, </t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>6202354688</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>29.861559</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>15.771</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>1.729</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OMAB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grupo Aeroportuario del Centro </t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>4810946560</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>15.744866</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>3.012</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="32">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="34">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="32">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>0.167</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>62</v>
+        <v>61.17</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0447700023651123</v>
+        <v>0.04456999778747558</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540362.32258064</v>
+        <v>52540361.09203858</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>62</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3257502464</v>
+        <v>3213893888</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.31</v>
+        <v>9.18</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.78</v>
+        <v>6.82</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.89</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4993132544</v>
+        <v>4885603840</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>91.44898000000001</v>
+        <v>89.47959</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.82</v>
+        <v>8.673</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.696</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4231350528</v>
+        <v>4251117568</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>24.007008</v>
+        <v>24.119158</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.406000000000001</v>
+        <v>8.359</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.361</v>
+        <v>1.353</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6170568192</v>
+        <v>6065123328</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.96</v>
+        <v>21.81</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>7231064576</v>
+        <v>7514345472</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>32.418766</v>
+        <v>33.68879</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>23.896</v>
+        <v>23.318</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.941</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="10">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8254842368</v>
+        <v>8622576640</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>29.319067</v>
+        <v>30.664936</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.631</v>
+        <v>15.626</v>
       </c>
       <c r="F10" s="33" t="n">
         <v>2.42</v>
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>79713008</v>
+        <v>79516664</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.301</v>
+        <v>-1.282</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.192</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6202354688</v>
+        <v>6412012032</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>29.861559</v>
+        <v>30.954176</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>15.771</v>
+        <v>16.091</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.729</v>
+        <v>1.764</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4810946560</v>
+        <v>4945502720</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>15.744866</v>
+        <v>16.185228</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>5</v>
+        <v>4.998</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>3.012</v>
+        <v>3.011</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.947</v>
+        <v>0.949</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>61.17</v>
+        <v>59.515</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.954</v>
+        <v>0.96</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04456999778747558</v>
+        <v>0.04497000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540361.09203858</v>
+        <v>52540362.05998488</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>61.17</v>
+        <v>59.515</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3213893888</v>
+        <v>3126939648</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.18</v>
+        <v>8.94</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.82</v>
+        <v>6.71</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4885603840</v>
+        <v>4719016960</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>89.47959</v>
+        <v>86.428566</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.673</v>
+        <v>8.613</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="7">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4251117568</v>
+        <v>4154136320</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>24.119158</v>
+        <v>23.568924</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.359</v>
+        <v>8.356999999999999</v>
       </c>
       <c r="F7" s="33" t="n">
         <v>1.353</v>
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6065123328</v>
+        <v>6207659520</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.81</v>
+        <v>21.88</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.83</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>7514345472</v>
+        <v>7773126144</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>33.68879</v>
+        <v>34.84897</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>23.318</v>
+        <v>24.212</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.894</v>
+        <v>1.967</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8622576640</v>
+        <v>8744910848</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>30.664936</v>
+        <v>31.1</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.626</v>
+        <v>16.231</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.42</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>79516664</v>
+        <v>74608224</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.282</v>
+        <v>-1.263</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.175</v>
+        <v>1.158</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6412012032</v>
+        <v>6470638592</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>30.954176</v>
+        <v>31.153225</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.091</v>
+        <v>16.528</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.764</v>
+        <v>1.812</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4945502720</v>
+        <v>4938141696</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>16.185228</v>
+        <v>16.212362</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>4.998</v>
+        <v>5.126</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>3.011</v>
+        <v>3.088</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-04 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>59.515</v>
+        <v>60.68</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.96</v>
+        <v>0.956</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04497000217437744</v>
+        <v>0.04470999717712403</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540362.05998488</v>
+        <v>52540363.34871457</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>59.515</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3126939648</v>
+        <v>3188149248</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.94</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.71</v>
+        <v>6.65</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4719016960</v>
+        <v>4665530880</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>86.428566</v>
+        <v>85.448975</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.613</v>
+        <v>8.413</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.68</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4154136320</v>
+        <v>4154548224</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>23.568924</v>
+        <v>23.57126</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.356999999999999</v>
+        <v>8.257999999999999</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.353</v>
+        <v>1.337</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6207659520</v>
+        <v>6213841408</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.88</v>
+        <v>21.914</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.839</v>
+        <v>2.844</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>7773126144</v>
+        <v>7928803328</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>34.84897</v>
+        <v>35.46575</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>24.212</v>
+        <v>24.409</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.967</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8744910848</v>
+        <v>8785003520</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>31.1</v>
+        <v>31.202063</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>16.231</v>
+        <v>16.396</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.513</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>74608224</v>
+        <v>93063952</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.263</v>
+        <v>-1.167</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.158</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6470638592</v>
+        <v>6563881472</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>31.153225</v>
+        <v>31.60215</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.528</v>
+        <v>16.799</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.812</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4938141696</v>
+        <v>4843529728</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>16.212362</v>
+        <v>15.901743</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>5.126</v>
+        <v>5.034</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>3.088</v>
+        <v>3.032</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-04 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.948</v>
+        <v>0.955</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>60.68</v>
+        <v>54.745</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.956</v>
+        <v>0.976</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04470999717712403</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540363.34871457</v>
+        <v>52540360.72700703</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>60.68</v>
+        <v>54.745</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3188149248</v>
+        <v>2876322048</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.109999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.65</v>
+        <v>6.26</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4665530880</v>
+        <v>5922450432</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>85.448975</v>
+        <v>108.46939</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.413</v>
+        <v>9.532</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.664</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4154548224</v>
+        <v>3906020352</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>23.57126</v>
+        <v>22.161213</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.257999999999999</v>
+        <v>7.989</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.337</v>
+        <v>1.293</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6213841408</v>
+        <v>5928327168</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.914</v>
+        <v>21.713</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.844</v>
+        <v>2.818</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>7928803328</v>
+        <v>8023740416</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>35.46575</v>
+        <v>35.97254</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>24.409</v>
+        <v>26.245</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.983</v>
+        <v>2.132</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8785003520</v>
+        <v>7949918720</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>31.202063</v>
+        <v>28.272728</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>16.396</v>
+        <v>15.529</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.539</v>
+        <v>2.404</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>93063952</v>
+        <v>80891024</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.167</v>
+        <v>-1.18</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.07</v>
+        <v>1.082</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6563881472</v>
+        <v>6546014720</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>31.60215</v>
+        <v>31.516129</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.799</v>
+        <v>17.086</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.842</v>
+        <v>1.873</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4843529728</v>
+        <v>5453435904</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>15.901743</v>
+        <v>18.13403</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>5.034</v>
+        <v>1.587</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>3.032</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>54.745</v>
+        <v>54.53</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.976</v>
+        <v>0.977</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04372</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540360.72700703</v>
+        <v>52540363.98312856</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>54.745</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2876322048</v>
+        <v>2865026048</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.220000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.26</v>
+        <v>6.22</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5922450432</v>
+        <v>6001564672</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>108.46939</v>
+        <v>109.918365</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.532</v>
+        <v>9.587999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>3906020352</v>
+        <v>3874722816</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.161213</v>
+        <v>21.983643</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>7.989</v>
+        <v>7.938</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.293</v>
+        <v>1.285</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>5928327168</v>
+        <v>5881256960</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.713</v>
+        <v>21.743</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.818</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>8023740416</v>
+        <v>7928292864</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>35.97254</v>
+        <v>35.626144</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>26.245</v>
+        <v>24.938</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.132</v>
+        <v>2.026</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>7949918720</v>
+        <v>8103293440</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>28.272728</v>
+        <v>28.818182</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.529</v>
+        <v>15.25</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.404</v>
+        <v>2.361</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>80891024</v>
+        <v>93063952</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.18</v>
+        <v>-1.48</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.082</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6546014720</v>
+        <v>6598498816</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>31.516129</v>
+        <v>31.768818</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>17.086</v>
+        <v>16.928</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.873</v>
+        <v>1.856</v>
       </c>
     </row>
     <row r="13">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5453435904</v>
+        <v>5405889024</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>18.13403</v>
+        <v>18.033815</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>1.587</v>

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>54.53</v>
+        <v>54.32</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.977</v>
+        <v>0.978</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04375999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540363.98312856</v>
+        <v>52540361.7083947</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>54.53</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2865026048</v>
+        <v>2853992448</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.19</v>
+        <v>8.16</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>6.22</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>6001564672</v>
+        <v>5716306432</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>109.918365</v>
+        <v>104.69387</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.587999999999999</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>3874722816</v>
+        <v>3766622464</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>21.983643</v>
+        <v>21.370325</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>7.938</v>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>5881256960</v>
+        <v>5568277504</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>7928292864</v>
+        <v>8054110208</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>35.626144</v>
+        <v>36.191513</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>24.938</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8103293440</v>
+        <v>8148210688</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>28.818182</v>
+        <v>28.977924</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>15.25</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>93063952</v>
+        <v>104647856</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6598498816</v>
+        <v>6516980736</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>31.768818</v>
+        <v>31.376345</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>16.928</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5405889024</v>
+        <v>5430990336</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>18.033815</v>
+        <v>18.117552</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>1.587</v>

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.955</v>
+        <v>0.95</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>54.32</v>
+        <v>58.85</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.978</v>
+        <v>0.962</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04375999927520752</v>
+        <v>0.04549000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540361.7083947</v>
+        <v>52540361.18946474</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>54.32</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2853992448</v>
+        <v>3092000256</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.16</v>
+        <v>8.84</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.22</v>
+        <v>6.46</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5716306432</v>
+        <v>5360847872</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>104.69387</v>
+        <v>98.18367000000001</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.587999999999999</v>
+        <v>8.903</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.757</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>3766622464</v>
+        <v>4606304256</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>21.370325</v>
+        <v>26.134346</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>7.938</v>
+        <v>8.647</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.285</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>5568277504</v>
+        <v>5609960448</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.743</v>
+        <v>21.588</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.821</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>8054110208</v>
+        <v>6966413824</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>36.191513</v>
+        <v>31.232265</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>24.938</v>
+        <v>22.231</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.026</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>8148210688</v>
+        <v>7392209408</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>28.977924</v>
+        <v>26.299612</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.25</v>
+        <v>14.071</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.361</v>
+        <v>2.179</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>104647856</v>
+        <v>76178928</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.48</v>
+        <v>-1.223</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.357</v>
+        <v>1.122</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6516980736</v>
+        <v>6958169088</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>31.376345</v>
+        <v>30.022892</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.928</v>
+        <v>16.693</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.856</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5430990336</v>
+        <v>5269764096</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>18.117552</v>
+        <v>17.4672</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>1.587</v>
+        <v>1.565</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.956</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>58.85</v>
+        <v>59.235</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.962</v>
+        <v>0.961</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04549000263214111</v>
+        <v>0.04572999954223633</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540361.18946474</v>
+        <v>52540366.47252469</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>58.85</v>
+        <v>59.235</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3092000256</v>
+        <v>3112228608</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.84</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.85</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5360847872</v>
+        <v>5289533440</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>98.18367000000001</v>
+        <v>96.87755</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.903</v>
+        <v>9.002000000000001</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.703</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4606304256</v>
+        <v>4795119104</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>26.134346</v>
+        <v>27.142193</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.647</v>
+        <v>8.776999999999999</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.4</v>
+        <v>1.421</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1580,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>5609960448</v>
+        <v>5492858368</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.588</v>
+        <v>21.614</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.801</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>6966413824</v>
+        <v>6859991552</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>31.232265</v>
+        <v>30.684929</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>22.231</v>
+        <v>22.259</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.806</v>
+        <v>1.808</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>7392209408</v>
+        <v>7080144896</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>26.299612</v>
+        <v>25.189365</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>14.071</v>
+        <v>14.136</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.179</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1650,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>76178928</v>
+        <v>73364760</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.223</v>
+        <v>-1.246</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.122</v>
+        <v>1.142</v>
       </c>
     </row>
     <row r="12">
@@ -1672,16 +1672,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>6958169088</v>
+        <v>6993352192</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>30.022892</v>
+        <v>30.247585</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.693</v>
+        <v>16.641</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.896</v>
+        <v>1.891</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5269764096</v>
+        <v>5136294400</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>17.4672</v>
+        <v>17.0248</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>1.565</v>
+        <v>1.566</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.95</v>
+        <v>0.896</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>59.235</v>
+        <v>59.75</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.961</v>
+        <v>0.967</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.944</v>
+        <v>0.861</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04572999954223633</v>
+        <v>0.0472</v>
       </c>
     </row>
     <row r="6">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>1627986048</v>
+        <v>1732647040</v>
       </c>
     </row>
     <row r="33">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>157452000</v>
+        <v>56953000</v>
       </c>
     </row>
     <row r="34">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52540366.47252469</v>
+        <v>52357762.67782427</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>59.235</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3112228608</v>
+        <v>3128376320</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.48</v>
+        <v>6.94</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5289533440</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>96.87755</v>
-      </c>
+        <v>4723043840</v>
+      </c>
+      <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>9.002000000000001</v>
+        <v>13.765</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.711</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4795119104</v>
+        <v>4569858560</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>27.142193</v>
+        <v>25.6875</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.776999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.421</v>
+        <v>1.386</v>
       </c>
     </row>
     <row r="8">
@@ -1580,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>5492858368</v>
+        <v>4879192576</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.614</v>
+        <v>21.837</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.805</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1600,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>6859991552</v>
+        <v>5907045376</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>30.684929</v>
+        <v>24.313025</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>22.259</v>
+        <v>16.73</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.808</v>
+        <v>1.433</v>
       </c>
     </row>
     <row r="10">
@@ -1626,16 +1624,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>7080144896</v>
+        <v>6688656896</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>25.189365</v>
+        <v>20.447632</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>14.136</v>
+        <v>11.72</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>2.189</v>
+        <v>1.916</v>
       </c>
     </row>
     <row r="11">
@@ -1650,14 +1648,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>73364760</v>
-      </c>
-      <c r="D11" s="33" t="n"/>
+        <v>80760136</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>0.31367564</v>
+      </c>
       <c r="E11" s="33" t="n">
-        <v>-1.246</v>
+        <v>-2.067</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.142</v>
+        <v>1.108</v>
       </c>
     </row>
     <row r="12">
@@ -1671,17 +1671,15 @@
           <t xml:space="preserve">MSC Industrial Direct Company, </t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>6993352192</v>
-      </c>
+      <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>30.247585</v>
+        <v>28.79227</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.641</v>
+        <v>16.075</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.891</v>
+        <v>1.826</v>
       </c>
     </row>
     <row r="13">
@@ -1696,16 +1694,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5136294400</v>
+        <v>4858976768</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>17.0248</v>
+        <v>15.182504</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>1.566</v>
+        <v>1.695</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.944</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="15">
@@ -1753,7 +1751,7 @@
         </is>
       </c>
       <c r="D17" s="35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E17" s="35" t="n">
         <v>0</v>

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0472</v>
+        <v>0.04719999790191651</v>
       </c>
     </row>
     <row r="6">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>28.79227</v>
+        <v>29.50495</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>16.075</v>

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.896</v>
+        <v>0.9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>59.75</v>
+        <v>56.44</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.967</v>
+        <v>0.978</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04719999790191651</v>
+        <v>0.04835000038146973</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52357762.67782427</v>
+        <v>52357764.98936924</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>59.75</v>
+        <v>56.44</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>3128376320</v>
+        <v>2955072256</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.84</v>
+        <v>8.35</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.94</v>
+        <v>6.68</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="6">
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4723043840</v>
+        <v>4504302080</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>13.765</v>
+        <v>13.515</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.655</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4569858560</v>
+        <v>4385573888</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>25.6875</v>
+        <v>24.65162</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.6</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.386</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>4879192576</v>
+        <v>4678895616</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.837</v>
+        <v>21.739</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.87</v>
+        <v>2.857</v>
       </c>
     </row>
     <row r="9">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>5907045376</v>
+        <v>5978248192</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>24.313025</v>
+        <v>23.519075</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>16.73</v>
+        <v>17.319</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.433</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="10">
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6688656896</v>
+        <v>6464330752</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>20.447632</v>
+        <v>19.211147</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>11.72</v>
+        <v>11.432</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.916</v>
+        <v>1.869</v>
       </c>
     </row>
     <row r="11">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>80760136</v>
+        <v>79189440</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.31367564</v>
+        <v>0.307575</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-2.067</v>
+        <v>-2.046</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.108</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="12">
@@ -1673,13 +1673,13 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>29.50495</v>
+        <v>28.805555</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.075</v>
+        <v>16.224</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.826</v>
+        <v>1.843</v>
       </c>
     </row>
     <row r="13">
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4858976768</v>
+        <v>4799844352</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>15.182504</v>
+        <v>14.952631</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>1.695</v>
+        <v>1.688</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>1.025</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/MMS_research.xlsx
+++ b/app/reports/MMS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>56.44</v>
+        <v>56.52</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04835000038146973</v>
+        <v>0.0492199993133545</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>52357764.98936924</v>
+        <v>52357765.88818117</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>56.44</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2955072256</v>
+        <v>2959260928</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>8.35</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.88</v>
@@ -1532,14 +1532,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4504302080</v>
+        <v>4480798208</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>13.515</v>
+        <v>13.454</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.644</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="7">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>4385573888</v>
+        <v>4483996160</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>24.65162</v>
+        <v>25.20486</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>8.343999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.345</v>
+        <v>1.366</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>4678895616</v>
+        <v>4518517248</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>21.739</v>
+        <v>21.711</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.857</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="9">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>5978248192</v>
+        <v>5828441088</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>23.519075</v>
+        <v>22.92972</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>17.319</v>
+        <v>16.947</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.484</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="10">
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6464330752</v>
+        <v>6484491264</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>19.211147</v>
+        <v>19.27106</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>11.432</v>
+        <v>11.35</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.869</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="11">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>79189440</v>
+        <v>79451224</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>0.307575</v>
+        <v>0.30859178</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-2.046</v>
+        <v>-1.962</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.096</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="12">
@@ -1673,13 +1673,13 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>28.805555</v>
+        <v>28.67633</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.224</v>
+        <v>16.104</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.843</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>4799844352</v>
+        <v>4759054848</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>14.952631</v>
+        <v>14.870286</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>1.688</v>
